--- a/data_fixed.xlsx
+++ b/data_fixed.xlsx
@@ -790,16 +790,22 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>AI監査システム</author>
+    <author>AI Agent</author>
   </authors>
   <commentList>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>【判定理由】: 負の値は入力不可です。
+【修正アドバイス】: 絶対値に修正しました。確認してください。</t>
+      </text>
+    </comment>
     <comment ref="D7" authorId="0" shapeId="0">
       <text>
         <t>【判定理由】: 負の値は入力不可です。
 【修正アドバイス】: 絶対値に修正しました。確認してください。</t>
       </text>
     </comment>
-    <comment ref="C10" authorId="0" shapeId="0">
+    <comment ref="D10" authorId="0" shapeId="0">
       <text>
         <t>【判定理由】: 姓名間にスペースが不足しています。
 【修正アドバイス】: スペースを補完しました。</t>
@@ -1182,7 +1188,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>佐藤 健一</t>
         </is>
@@ -1266,12 +1272,12 @@
       <c r="B10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>田中 太郎</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>300000</v>
       </c>
       <c r="E10" t="inlineStr">

--- a/data_fixed.xlsx
+++ b/data_fixed.xlsx
@@ -806,6 +806,12 @@
       </text>
     </comment>
     <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>【判定理由】: 姓名間にスペースが不足しています。
+【修正アドバイス】: スペースを補完しました。</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <t>【判定理由】: 姓名間にスペースが不足しています。
 【修正アドバイス】: スペースを補完しました。</t>
@@ -1280,7 +1286,7 @@
       <c r="D10" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
